--- a/data/valuebets_database_2025-07-28.xlsx
+++ b/data/valuebets_database_2025-07-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>01/08 19:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>55</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45866.08630208118</v>
+        <v>45866.08630208333</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>28/07 16:30</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>40</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45866.08630208118</v>
+        <v>45866.08630208333</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>02/08 16:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>40</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45866.08630208118</v>
+        <v>45866.08630208333</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>03/08 19:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>45</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45866.08630208118</v>
+        <v>45866.08630208333</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>03/08 00:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>50</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45866.08630208118</v>
+        <v>45866.08630208333</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>02/08 17:30</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>45</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45866.08630208118</v>
+        <v>45866.08630208333</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>03/08 23:30</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>55</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45866.08630208118</v>
+        <v>45866.08630208333</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>29/07 19:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>40</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45866.08630208118</v>
+        <v>45866.08630208333</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>31/07 19:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>45</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45866.08630208118</v>
+        <v>45866.08630208333</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>28/07 17:30</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="F11" t="n">
+        <v>2.1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,187 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45866.08630208118</v>
+        <v>45866.08630208333</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Rionegro A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Rionegro Aguilas – Fortaleza FCPrimera A</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>04/08 01:30</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>+23,3%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>45866.1719558037</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Atletico M</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Atletico Mineiro – Red Bull BragantinoSérie A</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>03/08 21:30</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>+2,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>45866.1719558037</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Basketball | Moins que 159.5P | Atlanta Dr</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Atlanta Dream – Golden State ValkyriesWNBA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Moins que 159.5P</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>29/07 23:30</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>55,0%</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>+0,64%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>45866.1719558037</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PokerStars(FR)Tennis | Moins que 11.52e participant | Eva Lys – </t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Eva Lys – Leol JeanjeanWTA Montréal 2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Moins que 11.52e participant</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>28/07 17:30</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>45,5%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>+0,02%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>45866.1719558037</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-28.xlsx
+++ b/data/valuebets_database_2025-07-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -935,10 +935,8 @@
           <t>04/08 01:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>45</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -951,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45866.1719558037</v>
+        <v>45866.17195579861</v>
       </c>
     </row>
     <row r="13">
@@ -980,10 +978,8 @@
           <t>03/08 21:30</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>50</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -996,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45866.1719558037</v>
+        <v>45866.17195579861</v>
       </c>
     </row>
     <row r="14">
@@ -1025,10 +1021,8 @@
           <t>29/07 23:30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
+      <c r="F14" t="n">
+        <v>1.83</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1041,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45866.1719558037</v>
+        <v>45866.17195579861</v>
       </c>
     </row>
     <row r="15">
@@ -1070,10 +1064,8 @@
           <t>28/07 17:30</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F15" t="n">
+        <v>2.2</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1086,7 +1078,52 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45866.1719558037</v>
+        <v>45866.17195579861</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 10.5 - tir cadré | Gremio RS </t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Gremio RS – Fortaleza CEBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Plus que 10.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>29/07 23:30</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>31,7%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>+4,52%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>45866.22999881147</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-28.xlsx
+++ b/data/valuebets_database_2025-07-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1107,10 +1107,8 @@
           <t>29/07 23:30</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="F16" t="n">
+        <v>3.3</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1123,7 +1121,52 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45866.22999881147</v>
+        <v>45866.22999880787</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 4.5 - tir cadré2e équipe | GKS Katowi</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GKS Katowice – Zagłębie LubinPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>28/07 17:00</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>39,4%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>+1,53%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>45866.27627234325</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-28.xlsx
+++ b/data/valuebets_database_2025-07-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1150,10 +1150,8 @@
           <t>28/07 17:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
+      <c r="F17" t="n">
+        <v>2.58</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1166,7 +1164,142 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45866.27627234325</v>
+        <v>45866.27627233796</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Club Olimp</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Club Olimpia – CD RecoletaPrimera Division</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>30/07 21:15</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>+48,3%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>45866.31097213621</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Malmo FF –</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Malmo FF – Rigas Futbola SkolaLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>30/07 17:00</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2,20%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>+32,3%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>45866.31097213621</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 3.51er set1er participant | Tristan Sc</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Tristan Schoolkate – Joao FonsecaATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Moins que 3.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>28/07 17:40</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>35,6%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>+10,2%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>45866.31097213621</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-28.xlsx
+++ b/data/valuebets_database_2025-07-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1193,10 +1193,8 @@
           <t>30/07 21:15</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>60</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1209,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45866.31097213621</v>
+        <v>45866.3109721412</v>
       </c>
     </row>
     <row r="19">
@@ -1238,10 +1236,8 @@
           <t>30/07 17:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>60</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1254,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45866.31097213621</v>
+        <v>45866.3109721412</v>
       </c>
     </row>
     <row r="20">
@@ -1283,10 +1279,8 @@
           <t>28/07 17:40</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F20" t="n">
+        <v>3.1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1299,7 +1293,322 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45866.31097213621</v>
+        <v>45866.3109721412</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | S.Cirstea </t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>S.Cirstea – L.SunWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>28/07 16:10</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>52,5%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>+18,2%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>45866.3573652739</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Ceara SC –</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ceara SC – FlamengoSérie A</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>03/08 21:30</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>+13,4%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>45866.3573652739</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | EG.Ruse – </t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EG.Ruse – E.RaducanuWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>28/07 16:30</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>43,8%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>+9,41%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>45866.3573652739</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | F.Marozsan</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>F.Marozsan – H.DellienATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>28/07 22:10</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>15,0%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>+4,74%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>45866.3573652739</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | X - aces | E.Lys – L.</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>E.Lys – L.JeanjeanWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>28/07 17:20</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>17,2%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>+2,89%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>45866.3573652739</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis | H 2 (−3.5)1er set | Ari Arsene</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ari Arseneault – N OsakaWTA Montréal 2025</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>H 2 (−3.5)1er set</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>28/07 18:00</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>51,3%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+2,57%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45866.3573652739</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Ferencvaro</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ferencvaros – FC NoahLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>30/07 18:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+2,17%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45866.3573652739</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-28.xlsx
+++ b/data/valuebets_database_2025-07-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1322,10 +1322,8 @@
           <t>28/07 16:10</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="F21" t="n">
+        <v>2.25</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1338,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45866.3573652739</v>
+        <v>45866.35736527778</v>
       </c>
     </row>
     <row r="22">
@@ -1367,10 +1365,8 @@
           <t>03/08 21:30</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>60</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1383,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45866.3573652739</v>
+        <v>45866.35736527778</v>
       </c>
     </row>
     <row r="23">
@@ -1412,10 +1408,8 @@
           <t>28/07 16:30</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F23" t="n">
+        <v>2.5</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1428,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45866.3573652739</v>
+        <v>45866.35736527778</v>
       </c>
     </row>
     <row r="24">
@@ -1457,10 +1451,8 @@
           <t>28/07 22:10</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>7</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1473,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45866.3573652739</v>
+        <v>45866.35736527778</v>
       </c>
     </row>
     <row r="25">
@@ -1502,10 +1494,8 @@
           <t>28/07 17:20</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>6</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1518,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45866.3573652739</v>
+        <v>45866.35736527778</v>
       </c>
     </row>
     <row r="26">
@@ -1547,10 +1537,8 @@
           <t>28/07 18:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>2</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1563,7 +1551,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45866.3573652739</v>
+        <v>45866.35736527778</v>
       </c>
     </row>
     <row r="27">
@@ -1592,10 +1580,8 @@
           <t>30/07 18:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>45</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1608,7 +1594,187 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45866.3573652739</v>
+        <v>45866.35736527778</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 4.51er set2e participant | Moyuka Uch</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Moyuka Uchijima – Marie BouzkovaWTA 1000 Montreal</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Moins que 4.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>28/07 16:10</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>25,6%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+7,67%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45866.39697152853</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Hajduk Spl</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Hajduk Split – Istra 1961HNL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>03/08 19:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+6,51%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45866.39697152853</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 3.51er set2e participant | Caroline D</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Caroline Dolehide – Anna BlinkovaWTA 1000 Montreal</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Moins que 3.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>28/07 16:10</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>36,1%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+2,95%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45866.39697152853</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 2 | Rapid Vien</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Rapid Vienne – Decic TuziEurope. Europa Conférence (Q)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>31/07 18:30</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+2,36%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45866.39697152853</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-28.xlsx
+++ b/data/valuebets_database_2025-07-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,10 +1623,8 @@
           <t>28/07 16:10</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="F28" t="n">
+        <v>4.2</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1639,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45866.39697152853</v>
+        <v>45866.39697152778</v>
       </c>
     </row>
     <row r="29">
@@ -1668,10 +1666,8 @@
           <t>03/08 19:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>50</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1684,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45866.39697152853</v>
+        <v>45866.39697152778</v>
       </c>
     </row>
     <row r="30">
@@ -1713,10 +1709,8 @@
           <t>28/07 16:10</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F30" t="n">
+        <v>2.85</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1729,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45866.39697152853</v>
+        <v>45866.39697152778</v>
       </c>
     </row>
     <row r="31">
@@ -1758,10 +1752,8 @@
           <t>31/07 18:30</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>30.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>30</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1774,7 +1766,232 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45866.39697152853</v>
+        <v>45866.39697152778</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Tennis | 2 - aces | Alexander </t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Alexander Blockx – Dalibor SvrcinaATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>28/07 16:10</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>18,0%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+43,7%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45866.43550143884</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PMU(FR)Tennis | H 1 (−6.5) | Comesana, </t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Comesana, Francisco – Dzumhur, DamirEvénements. ATP Toronto</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>H 1 (−6.5)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>28/07 17:20</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>16,3%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+22,5%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45866.43550143884</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Barnet FC </t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Barnet FC – Newport CountyEFL Cup</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>29/07 18:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+3,96%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45866.43550143884</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PokerStars(FR)Tennis | 11-21er set | Re Marino </t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Re Marino – Emm NavarroWTA Montréal 2025</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>11-21er set</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>29/07 00:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>26,4%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+3,03%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45866.43550143884</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | Y.Watanuki</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Y.Watanuki – D.AltmaierATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>28/07 16:10</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>51,4%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+2,86%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45866.43550143884</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-28.xlsx
+++ b/data/valuebets_database_2025-07-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,10 +1795,8 @@
           <t>28/07 16:10</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>8</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1811,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45866.43550143884</v>
+        <v>45866.43550143518</v>
       </c>
     </row>
     <row r="33">
@@ -1840,10 +1838,8 @@
           <t>28/07 17:20</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
+      <c r="F33" t="n">
+        <v>7.5</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1856,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45866.43550143884</v>
+        <v>45866.43550143518</v>
       </c>
     </row>
     <row r="34">
@@ -1885,10 +1881,8 @@
           <t>29/07 18:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>45</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1901,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45866.43550143884</v>
+        <v>45866.43550143518</v>
       </c>
     </row>
     <row r="35">
@@ -1930,10 +1924,8 @@
           <t>29/07 00:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="F35" t="n">
+        <v>3.9</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1946,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45866.43550143884</v>
+        <v>45866.43550143518</v>
       </c>
     </row>
     <row r="36">
@@ -1975,10 +1967,8 @@
           <t>28/07 16:10</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>2</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1991,7 +1981,187 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45866.43550143884</v>
+        <v>45866.43550143518</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | X - aces | R.Carballe</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>R.Carballes – U.CarabelliATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>28/07 18:30</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>15,2%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+21,9%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45866.47305701731</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Independie</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Independiente Medellin – Millonarios FCPrimera A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>03/08 23:20</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+10,9%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45866.47305701731</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 2 - aces | B.Coric – </t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>B.Coric – M.GiganteATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>28/07 21:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>42,7%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+6,74%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45866.47305701731</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Mattia Bel</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Mattia Bellucci – Hugo GastonATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>28/07 16:10</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>14,8%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+3,58%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45866.47305701731</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-28.xlsx
+++ b/data/valuebets_database_2025-07-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,10 +2010,8 @@
           <t>28/07 18:30</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>8</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2026,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45866.47305701731</v>
+        <v>45866.47305701389</v>
       </c>
     </row>
     <row r="38">
@@ -2055,10 +2053,8 @@
           <t>03/08 23:20</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>40</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2071,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45866.47305701731</v>
+        <v>45866.47305701389</v>
       </c>
     </row>
     <row r="39">
@@ -2100,10 +2096,8 @@
           <t>28/07 21:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F39" t="n">
+        <v>2.5</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2116,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45866.47305701731</v>
+        <v>45866.47305701389</v>
       </c>
     </row>
     <row r="40">
@@ -2145,10 +2139,8 @@
           <t>28/07 16:10</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>7</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2161,7 +2153,97 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45866.47305701731</v>
+        <v>45866.47305701389</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | OFK Belgra</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>OFK Belgrade – Javor IvanjicaSuperLiga</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>02/08 18:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+10,8%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45866.5356903279</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Liam Draxl</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Liam Draxl – Pablo Carreno-BustaATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>28/07 23:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>54,8%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+9,59%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45866.5356903279</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-28.xlsx
+++ b/data/valuebets_database_2025-07-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2182,10 +2182,8 @@
           <t>02/08 18:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>45</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2198,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45866.5356903279</v>
+        <v>45866.53569032408</v>
       </c>
     </row>
     <row r="42">
@@ -2227,10 +2225,8 @@
           <t>28/07 23:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>2</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2243,7 +2239,232 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45866.5356903279</v>
+        <v>45866.53569032408</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Zeleznicar</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Zeleznicar Pancevo – FK NapredakSuperLiga</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>03/08 17:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+47,2%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45866.57118398607</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 2 | Étoile Rou</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Étoile Rouge Belgrade – Lincoln Red ImpsEurope. Ligue des Champions (Q)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>29/07 19:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+38,9%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45866.57118398607</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | X - aces | K.Rakhimov</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>K.Rakhimova – K.CrossWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>28/07 15:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>19,7%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+18,4%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45866.57118398607</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Cukaricki </t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Cukaricki – Radnicki NisSuperLiga</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>04/08 19:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+8,95%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45866.57118398607</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Arthur Rin</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Arthur Rinderknech – Alexis GalarneauATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>29/07 00:10</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>10,7%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+7,04%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45866.57118398607</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-28.xlsx
+++ b/data/valuebets_database_2025-07-28.xlsx
@@ -2268,10 +2268,8 @@
           <t>03/08 17:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>55</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2284,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45866.57118398607</v>
+        <v>45866.57118398148</v>
       </c>
     </row>
     <row r="44">
@@ -2313,10 +2311,8 @@
           <t>29/07 19:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>60</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2329,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45866.57118398607</v>
+        <v>45866.57118398148</v>
       </c>
     </row>
     <row r="45">
@@ -2358,10 +2354,8 @@
           <t>28/07 15:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>6</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2374,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45866.57118398607</v>
+        <v>45866.57118398148</v>
       </c>
     </row>
     <row r="46">
@@ -2403,10 +2397,8 @@
           <t>04/08 19:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>40</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2419,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45866.57118398607</v>
+        <v>45866.57118398148</v>
       </c>
     </row>
     <row r="47">
@@ -2448,10 +2440,8 @@
           <t>29/07 00:10</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>10</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2464,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45866.57118398607</v>
+        <v>45866.57118398148</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-28.xlsx
+++ b/data/valuebets_database_2025-07-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2457,6 +2457,51 @@
         <v>45866.57118398148</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | X - aces | Y.Watanuki</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Y.Watanuki – D.AltmaierATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>28/07 16:10</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>13,0%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+4,20%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45866.64389992888</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-28.xlsx
+++ b/data/valuebets_database_2025-07-28.xlsx
@@ -2483,10 +2483,8 @@
           <t>28/07 16:10</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>8</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2499,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45866.64389992888</v>
+        <v>45866.64389993055</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-28.xlsx
+++ b/data/valuebets_database_2025-07-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2500,6 +2500,186 @@
         <v>45866.64389993055</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | T.Boyer – </t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>T.Boyer – A.KovacevicATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>28/07 18:30</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>36,6%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+2,55%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45866.72511512571</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 21-2- se qualifie | Maccabi Te</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Maccabi Tel Aviv – Pafos FCEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>30/07 18:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>37,0%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+1,67%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45866.72511512571</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | X - aces | A.Ruzic – </t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>A.Ruzic – A.PotapovaWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>28/07 23:10</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>16,9%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+1,66%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45866.72511512571</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | K.Boulter </t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>K.Boulter – R.ZarazuaWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>28/07 18:40</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>88,1%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+1,32%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45866.72511512571</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-28.xlsx
+++ b/data/valuebets_database_2025-07-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2526,10 +2526,8 @@
           <t>28/07 18:30</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F49" t="n">
+        <v>2.8</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2542,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45866.72511512571</v>
+        <v>45866.72511512732</v>
       </c>
     </row>
     <row r="50">
@@ -2571,10 +2569,8 @@
           <t>30/07 18:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F50" t="n">
+        <v>2.75</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2587,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45866.72511512571</v>
+        <v>45866.72511512732</v>
       </c>
     </row>
     <row r="51">
@@ -2616,10 +2612,8 @@
           <t>28/07 23:10</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>6</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2632,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45866.72511512571</v>
+        <v>45866.72511512732</v>
       </c>
     </row>
     <row r="52">
@@ -2661,10 +2655,8 @@
           <t>28/07 18:40</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
+      <c r="F52" t="n">
+        <v>1.15</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2677,7 +2669,52 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45866.72511512571</v>
+        <v>45866.72511512732</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Tie-break: Oui | Tristan Bo</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Tristan Boyer – Aleksandar KovacevicATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Tie-break: Oui</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>28/07 18:40</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>41,6%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+1,85%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45866.77492764078</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-28.xlsx
+++ b/data/valuebets_database_2025-07-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2698,10 +2698,8 @@
           <t>28/07 18:40</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="F53" t="n">
+        <v>2.45</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2714,7 +2712,52 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45866.77492764078</v>
+        <v>45866.77492763889</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Rapid Buca</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Rapid Bucarest – FC BotosaniLiga 1 - YYUZJR 385076e7</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>04/08 18:30</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+7,12%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45866.80604555897</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-28.xlsx
+++ b/data/valuebets_database_2025-07-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2741,10 +2741,8 @@
           <t>04/08 18:30</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>45</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2757,7 +2755,52 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45866.80604555897</v>
+        <v>45866.80604555555</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 5.51er set2e participant | Emilio Nav</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Emilio Nava – Ugo HumbertATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Moins que 5.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>29/07 15:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>24,4%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+2,59%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45866.85262639196</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-28.xlsx
+++ b/data/valuebets_database_2025-07-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2784,10 +2784,8 @@
           <t>29/07 15:00</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="F55" t="n">
+        <v>4.2</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2800,7 +2798,187 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45866.85262639196</v>
+        <v>45866.85262638889</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | Moins que 4.51er set2e participant | Aoi Ito – </t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Aoi Ito – Jasmine PaoliniWTA 1000 Montreal</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Moins que 4.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>29/07 15:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>6.70</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>15,3%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+2,38%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45866.89011262094</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 5.51er set1er participant | Lorenzo Mu</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Lorenzo Musetti – James DuckworthATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Moins que 5.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>29/07 17:40</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>20,7%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+1,45%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45866.89011262094</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | X2 | FC Arges –</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>FC Arges – CsikszeredaRoumanie - Roumanie Liga 1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>02/08 15:30</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>59,5%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+1,06%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45866.89011262094</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Pas de buts | Bodø/Glimt</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Bodø/Glimt – Strømsgodset IFNorvège - Norvège Eliteserien</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>30/07 17:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+0,54%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45866.89011262094</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-28.xlsx
+++ b/data/valuebets_database_2025-07-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,10 +2827,8 @@
           <t>29/07 15:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>6.70</t>
-        </is>
+      <c r="F56" t="n">
+        <v>6.7</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2843,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45866.89011262094</v>
+        <v>45866.89011261574</v>
       </c>
     </row>
     <row r="57">
@@ -2872,10 +2870,8 @@
           <t>29/07 17:40</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>4.90</t>
-        </is>
+      <c r="F57" t="n">
+        <v>4.9</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2888,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45866.89011262094</v>
+        <v>45866.89011261574</v>
       </c>
     </row>
     <row r="58">
@@ -2917,10 +2913,8 @@
           <t>02/08 15:30</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
+      <c r="F58" t="n">
+        <v>1.7</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2933,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45866.89011262094</v>
+        <v>45866.89011261574</v>
       </c>
     </row>
     <row r="59">
@@ -2962,10 +2956,8 @@
           <t>30/07 17:00</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>55</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2978,7 +2970,97 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45866.89011262094</v>
+        <v>45866.89011261574</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | San Lorenz</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>San Lorenzo – Velez SarsfieldLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>07/08 22:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+10,8%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45866.9336904752</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PMU(FR)Football | 21-2- se qualifie | FC Iberia </t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>FC Iberia 1999 – Levadia Tallinn385076e7 Europe. Europa Conférence (Q)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>29/07 16:00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>49,4%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+3,78%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45866.9336904752</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-28.xlsx
+++ b/data/valuebets_database_2025-07-28.xlsx
@@ -2999,10 +2999,8 @@
           <t>07/08 22:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>45</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3015,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45866.9336904752</v>
+        <v>45866.93369047454</v>
       </c>
     </row>
     <row r="61">
@@ -3044,10 +3042,8 @@
           <t>29/07 16:00</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="F61" t="n">
+        <v>2.1</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3060,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45866.9336904752</v>
+        <v>45866.93369047454</v>
       </c>
     </row>
   </sheetData>
